--- a/public/sap-reporting/expansion-150-downloads/EXT-FI22-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI22-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R427da3a12cd6467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2f8a6de9e6af4fe9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R5ac31fde4bed4cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3b612661dbb34505"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R0d4faf461fda4fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R66ca61eda2774962"/>
   </x:sheets>
 </x:workbook>
 </file>
